--- a/Team-Data/2013-14/2-27-2013-14.xlsx
+++ b/Team-Data/2013-14/2-27-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,10 +806,10 @@
         <v>-0.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF2" t="n">
         <v>18</v>
@@ -751,7 +818,7 @@
         <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI2" t="n">
         <v>16</v>
@@ -784,7 +851,7 @@
         <v>29</v>
       </c>
       <c r="AS2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT2" t="n">
         <v>27</v>
@@ -793,7 +860,7 @@
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW2" t="n">
         <v>7</v>
@@ -802,7 +869,7 @@
         <v>23</v>
       </c>
       <c r="AY2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ2" t="n">
         <v>4</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -948,7 +1015,7 @@
         <v>25</v>
       </c>
       <c r="AM3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AN3" t="n">
         <v>28</v>
@@ -957,7 +1024,7 @@
         <v>25</v>
       </c>
       <c r="AP3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ3" t="n">
         <v>11</v>
@@ -969,7 +1036,7 @@
         <v>20</v>
       </c>
       <c r="AT3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU3" t="n">
         <v>27</v>
@@ -981,7 +1048,7 @@
         <v>22</v>
       </c>
       <c r="AX3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY3" t="n">
         <v>14</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -1025,52 +1092,52 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F4" t="n">
         <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>0.482</v>
+        <v>0.473</v>
       </c>
       <c r="H4" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="J4" t="n">
-        <v>78.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="K4" t="n">
         <v>0.45</v>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M4" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="N4" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="O4" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P4" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.763</v>
+        <v>0.761</v>
       </c>
       <c r="R4" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="S4" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="T4" t="n">
         <v>38.9</v>
@@ -1091,31 +1158,31 @@
         <v>4.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AA4" t="n">
         <v>20.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>97.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.4</v>
+        <v>-2.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF4" t="n">
         <v>15</v>
       </c>
       <c r="AG4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
         <v>28</v>
@@ -1124,13 +1191,13 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL4" t="n">
         <v>14</v>
       </c>
       <c r="AM4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AN4" t="n">
         <v>13</v>
@@ -1139,16 +1206,16 @@
         <v>8</v>
       </c>
       <c r="AP4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ4" t="n">
         <v>13</v>
       </c>
       <c r="AR4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT4" t="n">
         <v>29</v>
@@ -1160,7 +1227,7 @@
         <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX4" t="n">
         <v>26</v>
@@ -1178,7 +1245,7 @@
         <v>22</v>
       </c>
       <c r="BC4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-1.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
         <v>16</v>
@@ -1294,7 +1361,7 @@
         <v>17</v>
       </c>
       <c r="AG5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH5" t="n">
         <v>14</v>
@@ -1303,7 +1370,7 @@
         <v>27</v>
       </c>
       <c r="AJ5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK5" t="n">
         <v>25</v>
@@ -1327,7 +1394,7 @@
         <v>26</v>
       </c>
       <c r="AR5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS5" t="n">
         <v>7</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -1467,13 +1534,13 @@
         <v>0.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
       </c>
       <c r="AF6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG6" t="n">
         <v>13</v>
@@ -1512,7 +1579,7 @@
         <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT6" t="n">
         <v>7</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1731,7 @@
         <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ7" t="n">
         <v>5</v>
@@ -1715,7 +1782,7 @@
         <v>27</v>
       </c>
       <c r="AZ7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA7" t="n">
         <v>18</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1934,7 @@
         <v>17</v>
       </c>
       <c r="AP8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ8" t="n">
         <v>2</v>
@@ -1900,7 +1967,7 @@
         <v>9</v>
       </c>
       <c r="BA8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB8" t="n">
         <v>7</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -1935,49 +2002,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E9" t="n">
         <v>25</v>
       </c>
       <c r="F9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G9" t="n">
-        <v>0.439</v>
+        <v>0.446</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
       </c>
       <c r="I9" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J9" t="n">
-        <v>85.2</v>
+        <v>85.3</v>
       </c>
       <c r="K9" t="n">
-        <v>0.442</v>
+        <v>0.444</v>
       </c>
       <c r="L9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0.358</v>
+        <v>0.359</v>
       </c>
       <c r="O9" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="P9" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="Q9" t="n">
         <v>0.719</v>
       </c>
       <c r="R9" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="S9" t="n">
         <v>33</v>
@@ -1986,13 +2053,13 @@
         <v>45.6</v>
       </c>
       <c r="U9" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="V9" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="W9" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X9" t="n">
         <v>5.8</v>
@@ -2007,19 +2074,19 @@
         <v>21.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.3</v>
+        <v>102.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2.4</v>
+        <v>-2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AE9" t="n">
         <v>19</v>
       </c>
       <c r="AF9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG9" t="n">
         <v>19</v>
@@ -2028,7 +2095,7 @@
         <v>27</v>
       </c>
       <c r="AI9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ9" t="n">
         <v>6</v>
@@ -2037,7 +2104,7 @@
         <v>21</v>
       </c>
       <c r="AL9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AM9" t="n">
         <v>9</v>
@@ -2058,28 +2125,28 @@
         <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT9" t="n">
         <v>5</v>
       </c>
       <c r="AU9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW9" t="n">
         <v>24</v>
       </c>
       <c r="AX9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY9" t="n">
         <v>24</v>
       </c>
       <c r="AZ9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA9" t="n">
         <v>7</v>
@@ -2088,7 +2155,7 @@
         <v>11</v>
       </c>
       <c r="BC9" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2283,7 @@
         <v>4</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL10" t="n">
         <v>28</v>
@@ -2261,7 +2328,7 @@
         <v>16</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA10" t="n">
         <v>15</v>
@@ -2270,7 +2337,7 @@
         <v>14</v>
       </c>
       <c r="BC10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2641,7 @@
         <v>16</v>
       </c>
       <c r="AI12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ12" t="n">
         <v>28</v>
@@ -2619,7 +2686,7 @@
         <v>17</v>
       </c>
       <c r="AX12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY12" t="n">
         <v>21</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F13" t="n">
         <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>0.772</v>
+        <v>0.768</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
@@ -2681,19 +2748,19 @@
         <v>36.9</v>
       </c>
       <c r="J13" t="n">
-        <v>81.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L13" t="n">
         <v>6.9</v>
       </c>
       <c r="M13" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.353</v>
+        <v>0.352</v>
       </c>
       <c r="O13" t="n">
         <v>18.4</v>
@@ -2702,7 +2769,7 @@
         <v>23.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.781</v>
+        <v>0.779</v>
       </c>
       <c r="R13" t="n">
         <v>10.4</v>
@@ -2714,7 +2781,7 @@
         <v>45.7</v>
       </c>
       <c r="U13" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V13" t="n">
         <v>15.4</v>
@@ -2723,25 +2790,25 @@
         <v>7.2</v>
       </c>
       <c r="X13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y13" t="n">
         <v>4.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA13" t="n">
         <v>21.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>99.2</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2759,7 +2826,7 @@
         <v>21</v>
       </c>
       <c r="AJ13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK13" t="n">
         <v>12</v>
@@ -2768,7 +2835,7 @@
         <v>21</v>
       </c>
       <c r="AM13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AN13" t="n">
         <v>20</v>
@@ -2795,22 +2862,22 @@
         <v>24</v>
       </c>
       <c r="AV13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AW13" t="n">
         <v>23</v>
       </c>
       <c r="AX13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA13" t="n">
         <v>5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>6</v>
       </c>
       <c r="BB13" t="n">
         <v>19</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2993,7 @@
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF14" t="n">
         <v>7</v>
@@ -2947,7 +3014,7 @@
         <v>6</v>
       </c>
       <c r="AL14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM14" t="n">
         <v>8</v>
@@ -2998,7 +3065,7 @@
         <v>2</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3226,7 @@
         <v>9</v>
       </c>
       <c r="AV15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>0.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
@@ -3326,7 +3393,7 @@
         <v>28</v>
       </c>
       <c r="AQ16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR16" t="n">
         <v>14</v>
@@ -3335,7 +3402,7 @@
         <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU16" t="n">
         <v>15</v>
@@ -3347,7 +3414,7 @@
         <v>16</v>
       </c>
       <c r="AX16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY16" t="n">
         <v>22</v>
@@ -3362,7 +3429,7 @@
         <v>28</v>
       </c>
       <c r="BC16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -3391,67 +3458,67 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F17" t="n">
         <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>0.745</v>
+        <v>0.741</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
       </c>
       <c r="I17" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="J17" t="n">
         <v>76.90000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.509</v>
+        <v>0.508</v>
       </c>
       <c r="L17" t="n">
         <v>8.1</v>
       </c>
       <c r="M17" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="N17" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="O17" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="P17" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.756</v>
+        <v>0.757</v>
       </c>
       <c r="R17" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="S17" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T17" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="U17" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="V17" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y17" t="n">
         <v>3</v>
@@ -3463,25 +3530,25 @@
         <v>20.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>104.2</v>
+        <v>104.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="AD17" t="n">
         <v>30</v>
       </c>
       <c r="AE17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF17" t="n">
         <v>2</v>
       </c>
       <c r="AG17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI17" t="n">
         <v>4</v>
@@ -3496,10 +3563,10 @@
         <v>12</v>
       </c>
       <c r="AM17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AN17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO17" t="n">
         <v>14</v>
@@ -3526,7 +3593,7 @@
         <v>16</v>
       </c>
       <c r="AW17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX17" t="n">
         <v>21</v>
@@ -3535,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
         <v>12</v>
@@ -3544,7 +3611,7 @@
         <v>8</v>
       </c>
       <c r="BC17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -3573,43 +3640,43 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E18" t="n">
         <v>11</v>
       </c>
       <c r="F18" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G18" t="n">
-        <v>0.193</v>
+        <v>0.196</v>
       </c>
       <c r="H18" t="n">
         <v>48.6</v>
       </c>
       <c r="I18" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="J18" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="K18" t="n">
         <v>0.426</v>
       </c>
       <c r="L18" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M18" t="n">
         <v>20.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0.358</v>
+        <v>0.355</v>
       </c>
       <c r="O18" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="P18" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="Q18" t="n">
         <v>0.751</v>
@@ -3618,16 +3685,16 @@
         <v>11.7</v>
       </c>
       <c r="S18" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T18" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U18" t="n">
         <v>21.1</v>
       </c>
       <c r="V18" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W18" t="n">
         <v>6.8</v>
@@ -3642,16 +3709,16 @@
         <v>20.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB18" t="n">
         <v>93.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3663,7 +3730,7 @@
         <v>30</v>
       </c>
       <c r="AH18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI18" t="n">
         <v>29</v>
@@ -3681,16 +3748,16 @@
         <v>17</v>
       </c>
       <c r="AN18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP18" t="n">
         <v>27</v>
       </c>
       <c r="AQ18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR18" t="n">
         <v>12</v>
@@ -3702,10 +3769,10 @@
         <v>25</v>
       </c>
       <c r="AU18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>4</v>
       </c>
       <c r="AD19" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
         <v>15</v>
@@ -3860,7 +3927,7 @@
         <v>16</v>
       </c>
       <c r="AM19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN19" t="n">
         <v>25</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
         <v>20</v>
@@ -4063,7 +4130,7 @@
         <v>26</v>
       </c>
       <c r="AT20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU20" t="n">
         <v>16</v>
@@ -4072,7 +4139,7 @@
         <v>6</v>
       </c>
       <c r="AW20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX20" t="n">
         <v>1</v>
@@ -4084,13 +4151,13 @@
         <v>27</v>
       </c>
       <c r="BA20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB20" t="n">
         <v>20</v>
       </c>
       <c r="BC20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -4119,58 +4186,58 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E21" t="n">
         <v>21</v>
       </c>
       <c r="F21" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G21" t="n">
-        <v>0.362</v>
+        <v>0.368</v>
       </c>
       <c r="H21" t="n">
         <v>48.6</v>
       </c>
       <c r="I21" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="J21" t="n">
         <v>83.09999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.444</v>
+        <v>0.446</v>
       </c>
       <c r="L21" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="M21" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="N21" t="n">
-        <v>0.366</v>
+        <v>0.369</v>
       </c>
       <c r="O21" t="n">
         <v>14.7</v>
       </c>
       <c r="P21" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="Q21" t="n">
         <v>0.748</v>
       </c>
       <c r="R21" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S21" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T21" t="n">
         <v>40.7</v>
       </c>
       <c r="U21" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V21" t="n">
         <v>13.1</v>
@@ -4191,25 +4258,25 @@
         <v>19.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>97.59999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.4</v>
+        <v>-1.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE21" t="n">
         <v>23</v>
       </c>
       <c r="AF21" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI21" t="n">
         <v>20</v>
@@ -4227,7 +4294,7 @@
         <v>5</v>
       </c>
       <c r="AN21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4239,10 +4306,10 @@
         <v>22</v>
       </c>
       <c r="AR21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT21" t="n">
         <v>26</v>
@@ -4257,22 +4324,22 @@
         <v>14</v>
       </c>
       <c r="AX21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ21" t="n">
         <v>26</v>
       </c>
       <c r="BA21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB21" t="n">
         <v>21</v>
       </c>
       <c r="BC21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -4382,13 +4449,13 @@
         <v>6</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF22" t="n">
         <v>3</v>
       </c>
       <c r="AG22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="n">
         <v>26</v>
@@ -4397,7 +4464,7 @@
         <v>5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK22" t="n">
         <v>5</v>
@@ -4409,7 +4476,7 @@
         <v>16</v>
       </c>
       <c r="AN22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
@@ -4430,7 +4497,7 @@
         <v>8</v>
       </c>
       <c r="AU22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV22" t="n">
         <v>28</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -4597,7 +4664,7 @@
         <v>24</v>
       </c>
       <c r="AP23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ23" t="n">
         <v>12</v>
@@ -4609,7 +4676,7 @@
         <v>10</v>
       </c>
       <c r="AT23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU23" t="n">
         <v>20</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -4755,10 +4822,10 @@
         <v>29</v>
       </c>
       <c r="AH24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ24" t="n">
         <v>1</v>
@@ -4770,7 +4837,7 @@
         <v>22</v>
       </c>
       <c r="AM24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN24" t="n">
         <v>30</v>
@@ -4800,7 +4867,7 @@
         <v>30</v>
       </c>
       <c r="AW24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX24" t="n">
         <v>27</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
@@ -4937,7 +5004,7 @@
         <v>10</v>
       </c>
       <c r="AH25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI25" t="n">
         <v>9</v>
@@ -4955,7 +5022,7 @@
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO25" t="n">
         <v>11</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5177,7 @@
         <v>6</v>
       </c>
       <c r="AE26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF26" t="n">
         <v>5</v>
@@ -5137,7 +5204,7 @@
         <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -5289,19 +5356,19 @@
         <v>-2.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
       </c>
       <c r="AF27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG27" t="n">
         <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI27" t="n">
         <v>19</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>5.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5483,13 +5550,13 @@
         <v>4</v>
       </c>
       <c r="AH28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5519,7 +5586,7 @@
         <v>6</v>
       </c>
       <c r="AT28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU28" t="n">
         <v>2</v>
@@ -5540,13 +5607,13 @@
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB28" t="n">
         <v>9</v>
       </c>
       <c r="BC28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -5575,25 +5642,25 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E29" t="n">
         <v>32</v>
       </c>
       <c r="F29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G29" t="n">
-        <v>0.552</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>48.7</v>
+        <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>36.4</v>
+        <v>36.2</v>
       </c>
       <c r="J29" t="n">
-        <v>82.59999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="K29" t="n">
         <v>0.44</v>
@@ -5602,16 +5669,16 @@
         <v>8.300000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="N29" t="n">
         <v>0.363</v>
       </c>
       <c r="O29" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="P29" t="n">
-        <v>24.6</v>
+        <v>24.4</v>
       </c>
       <c r="Q29" t="n">
         <v>0.775</v>
@@ -5620,40 +5687,40 @@
         <v>11.8</v>
       </c>
       <c r="S29" t="n">
-        <v>31.3</v>
+        <v>31.1</v>
       </c>
       <c r="T29" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="U29" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V29" t="n">
         <v>14.1</v>
       </c>
       <c r="W29" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X29" t="n">
         <v>4.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>100.1</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE29" t="n">
         <v>11</v>
@@ -5665,19 +5732,19 @@
         <v>12</v>
       </c>
       <c r="AH29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AI29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AK29" t="n">
         <v>23</v>
       </c>
       <c r="AL29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM29" t="n">
         <v>10</v>
@@ -5689,7 +5756,7 @@
         <v>7</v>
       </c>
       <c r="AP29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ29" t="n">
         <v>10</v>
@@ -5701,10 +5768,10 @@
         <v>21</v>
       </c>
       <c r="AT29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV29" t="n">
         <v>9</v>
@@ -5716,16 +5783,16 @@
         <v>22</v>
       </c>
       <c r="AY29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-5.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE30" t="n">
         <v>23</v>
@@ -5877,7 +5944,7 @@
         <v>17</v>
       </c>
       <c r="AR30" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AS30" t="n">
         <v>23</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
@@ -5939,28 +6006,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F31" t="n">
         <v>28</v>
       </c>
       <c r="G31" t="n">
-        <v>0.517</v>
+        <v>0.509</v>
       </c>
       <c r="H31" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="I31" t="n">
-        <v>38.4</v>
+        <v>38.2</v>
       </c>
       <c r="J31" t="n">
-        <v>84.90000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="K31" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="L31" t="n">
         <v>7.8</v>
@@ -5969,55 +6036,55 @@
         <v>20.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0.38</v>
+        <v>0.383</v>
       </c>
       <c r="O31" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="P31" t="n">
-        <v>21.4</v>
+        <v>21.1</v>
       </c>
       <c r="Q31" t="n">
         <v>0.728</v>
       </c>
       <c r="R31" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="S31" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T31" t="n">
-        <v>42.6</v>
+        <v>42.3</v>
       </c>
       <c r="U31" t="n">
         <v>23.2</v>
       </c>
       <c r="V31" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W31" t="n">
         <v>8.6</v>
       </c>
       <c r="X31" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y31" t="n">
         <v>3.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.7</v>
+        <v>19.4</v>
       </c>
       <c r="AB31" t="n">
-        <v>100.2</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC31" t="n">
         <v>0.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6032,7 +6099,7 @@
         <v>1</v>
       </c>
       <c r="AI31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ31" t="n">
         <v>8</v>
@@ -6047,25 +6114,25 @@
         <v>19</v>
       </c>
       <c r="AN31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP31" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AQ31" t="n">
         <v>25</v>
       </c>
       <c r="AR31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT31" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AU31" t="n">
         <v>8</v>
@@ -6077,22 +6144,22 @@
         <v>6</v>
       </c>
       <c r="AX31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY31" t="n">
         <v>7</v>
       </c>
       <c r="AZ31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA31" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BB31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-27-2013-14</t>
+          <t>2014-02-27</t>
         </is>
       </c>
     </row>
